--- a/data/trans_orig/IQ18C_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos</t>
+          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos (tasa de respuesta: 95,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +716,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,97; 14,39</t>
+          <t>12,07; 14,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 12,95</t>
+          <t>10,88; 12,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 12,5</t>
+          <t>10,67; 12,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,11</t>
+          <t>7,75; 11,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 15,23</t>
+          <t>12,36; 15,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 12,85</t>
+          <t>10,59; 12,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 13,28</t>
+          <t>10,78; 13,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +756,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,55; 14,44</t>
+          <t>12,48; 14,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,02; 12,51</t>
+          <t>11,03; 12,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,95; 12,38</t>
+          <t>10,94; 12,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 11,99</t>
+          <t>9,74; 11,98</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,39; 15,05</t>
+          <t>13,43; 15,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 13,0</t>
+          <t>11,01; 12,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,22</t>
+          <t>11,21; 13,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 23,15</t>
+          <t>11,47; 24,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 14,54</t>
+          <t>13,01; 14,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,02; 13,05</t>
+          <t>11,05; 12,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 12,38</t>
+          <t>10,63; 12,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,11; 14,07</t>
+          <t>10,16; 14,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 14,52</t>
+          <t>13,39; 14,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 12,59</t>
+          <t>11,24; 12,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,05; 12,35</t>
+          <t>11,1; 12,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,59; 17,64</t>
+          <t>11,72; 17,89</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,09; 15,31</t>
+          <t>13,17; 15,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 14,47</t>
+          <t>11,38; 14,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,21; 13,46</t>
+          <t>11,19; 13,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,52; 14,26</t>
+          <t>9,51; 14,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,28; 16,27</t>
+          <t>13,16; 16,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,91; 13,04</t>
+          <t>10,87; 13,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 13,54</t>
+          <t>10,85; 13,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,66; 18,46</t>
+          <t>10,46; 17,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,53; 15,48</t>
+          <t>13,54; 15,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,41; 13,31</t>
+          <t>11,39; 13,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,29; 12,97</t>
+          <t>11,37; 12,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,75; 15,36</t>
+          <t>10,68; 15,15</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,55; 15,69</t>
+          <t>13,4; 15,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 13,46</t>
+          <t>10,86; 13,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 11,03</t>
+          <t>9,41; 11,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,74; 23,57</t>
+          <t>13,42; 23,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,21; 15,51</t>
+          <t>13,28; 15,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 13,67</t>
+          <t>11,29; 13,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 14,1</t>
+          <t>11,63; 14,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,09; 16,09</t>
+          <t>10,96; 16,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,52; 15,11</t>
+          <t>13,61; 15,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,42; 13,21</t>
+          <t>11,42; 13,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 12,27</t>
+          <t>10,76; 12,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,68; 17,71</t>
+          <t>12,62; 17,52</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,53; 14,59</t>
+          <t>13,59; 14,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,65</t>
+          <t>11,47; 12,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,07</t>
+          <t>11,08; 12,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,8</t>
+          <t>11,82; 16,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 14,51</t>
+          <t>13,41; 14,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,5</t>
+          <t>11,39; 12,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,33; 12,45</t>
+          <t>11,37; 12,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,51; 14,38</t>
+          <t>11,45; 14,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 14,37</t>
+          <t>13,63; 14,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 12,38</t>
+          <t>11,59; 12,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,32; 12,11</t>
+          <t>11,34; 12,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,08; 14,49</t>
+          <t>12,16; 14,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Edad-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,07; 14,54</t>
+          <t>11,94; 14,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 12,87</t>
+          <t>11,0; 12,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 12,39</t>
+          <t>10,69; 12,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 11,17</t>
+          <t>7,76; 11,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 15,3</t>
+          <t>12,28; 15,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 12,83</t>
+          <t>10,6; 12,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 13,08</t>
+          <t>10,67; 13,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,69; 13,6</t>
+          <t>10,92; 13,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,48; 14,49</t>
+          <t>12,51; 14,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,03; 12,48</t>
+          <t>10,99; 12,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,94; 12,46</t>
+          <t>10,98; 12,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 11,98</t>
+          <t>9,5; 11,95</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,43; 15,02</t>
+          <t>13,42; 15,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,01; 12,81</t>
+          <t>11,0; 12,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 13,2</t>
+          <t>11,22; 13,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 24,29</t>
+          <t>11,66; 24,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,01; 14,57</t>
+          <t>12,99; 14,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,05; 12,98</t>
+          <t>10,97; 12,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 12,31</t>
+          <t>10,56; 12,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,16; 14,02</t>
+          <t>10,46; 14,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,39; 14,48</t>
+          <t>13,39; 14,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,24; 12,52</t>
+          <t>11,24; 12,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,1; 12,43</t>
+          <t>11,06; 12,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 17,89</t>
+          <t>11,47; 17,81</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,17; 15,38</t>
+          <t>13,21; 15,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 14,2</t>
+          <t>11,35; 14,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 13,43</t>
+          <t>11,15; 13,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 14,28</t>
+          <t>9,47; 14,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,16; 16,27</t>
+          <t>13,34; 16,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,87; 13,21</t>
+          <t>10,84; 13,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 13,31</t>
+          <t>10,96; 13,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,46; 17,7</t>
+          <t>10,77; 18,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,54; 15,41</t>
+          <t>13,56; 15,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 13,22</t>
+          <t>11,35; 13,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,98</t>
+          <t>11,36; 13,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,68; 15,15</t>
+          <t>10,8; 15,27</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,4; 15,54</t>
+          <t>13,54; 15,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,86; 13,45</t>
+          <t>10,9; 13,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 11,15</t>
+          <t>9,41; 11,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,42; 23,99</t>
+          <t>13,41; 24,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,4</t>
+          <t>13,28; 15,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 13,63</t>
+          <t>11,35; 13,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,63; 14,03</t>
+          <t>11,57; 14,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 16,01</t>
+          <t>10,84; 16,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,61; 15,13</t>
+          <t>13,66; 15,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,42; 13,08</t>
+          <t>11,43; 13,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 12,24</t>
+          <t>10,75; 12,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,62; 17,52</t>
+          <t>12,16; 17,31</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,59; 14,57</t>
+          <t>13,58; 14,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,63</t>
+          <t>11,47; 12,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,05</t>
+          <t>11,07; 12,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 16,51</t>
+          <t>12,02; 16,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,41; 14,53</t>
+          <t>13,46; 14,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 12,49</t>
+          <t>11,37; 12,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,49</t>
+          <t>11,29; 12,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,45; 14,27</t>
+          <t>11,61; 14,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 14,42</t>
+          <t>13,67; 14,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 12,37</t>
+          <t>11,58; 12,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,34; 12,09</t>
+          <t>11,36; 12,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,16; 14,55</t>
+          <t>12,12; 14,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Edad-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos (tasa de respuesta: 95,27%)</t>
+          <t>Tiempo medio en minutos que dura el trayecto desde su domicilio a la consulta médica (tasa de respuesta: 95,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,52</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,79</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12,02</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13,16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,81</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11,46</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,36</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,51</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,52</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,79</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,19</t>
+          <t>9,25</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,83</t>
+          <t>10,62</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,94; 14,33</t>
+          <t>12,28; 15,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 12,95</t>
+          <t>10,62; 12,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,69; 12,33</t>
+          <t>10,7; 13,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 11,08</t>
+          <t>10,49; 13,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 15,56</t>
+          <t>11,97; 14,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 12,89</t>
+          <t>10,91; 12,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 13,24</t>
+          <t>10,71; 12,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,92; 13,63</t>
+          <t>7,67; 11,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,51; 14,36</t>
+          <t>12,55; 14,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 12,52</t>
+          <t>11,02; 12,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 12,46</t>
+          <t>10,95; 12,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 11,95</t>
+          <t>9,49; 11,84</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,88</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11,31</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,28</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>14,14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,81</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>12,07</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,39</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,64</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,88</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,31</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,06</t>
+          <t>15,62</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,6</t>
+          <t>13,86</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,42; 15,07</t>
+          <t>12,93; 14,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,0; 12,96</t>
+          <t>11,02; 13,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 13,24</t>
+          <t>10,61; 12,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 24,02</t>
+          <t>10,34; 14,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,99; 14,52</t>
+          <t>13,39; 15,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 12,94</t>
+          <t>10,98; 13,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 12,22</t>
+          <t>11,2; 13,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,46; 14,31</t>
+          <t>11,51; 23,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,39; 14,47</t>
+          <t>13,38; 14,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,24; 12,53</t>
+          <t>11,18; 12,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,06; 12,37</t>
+          <t>11,05; 12,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 17,81</t>
+          <t>11,75; 17,81</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14,52</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,79</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,97</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13,72</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>14,17</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12,63</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>12,12</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,43</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,52</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,79</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,97</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,49</t>
+          <t>11,14</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,54</t>
+          <t>12,55</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,21; 15,62</t>
+          <t>13,28; 16,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,35; 14,03</t>
+          <t>10,91; 13,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 13,41</t>
+          <t>10,99; 13,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 14,05</t>
+          <t>10,89; 18,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,34; 16,37</t>
+          <t>13,09; 15,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 13,09</t>
+          <t>11,36; 14,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 13,43</t>
+          <t>11,21; 13,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 18,76</t>
+          <t>9,31; 14,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,56; 15,36</t>
+          <t>13,53; 15,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,35; 13,19</t>
+          <t>11,41; 13,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 13,07</t>
+          <t>11,29; 12,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 15,27</t>
+          <t>10,72; 15,44</t>
         </is>
       </c>
     </row>
@@ -1068,44 +1068,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,38</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,66</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13,15</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>14,38</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11,94</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10,19</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>17,42</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,18</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,38</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,66</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12,91</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14,28</t>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,84</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,54; 15,68</t>
+          <t>13,21; 15,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,9; 13,43</t>
+          <t>11,36; 13,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 11,12</t>
+          <t>11,58; 14,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 24,1</t>
+          <t>11,27; 16,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,5</t>
+          <t>13,55; 15,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 13,62</t>
+          <t>10,88; 13,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,57; 14,11</t>
+          <t>9,45; 11,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 16,1</t>
+          <t>13,6; 23,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 15,24</t>
+          <t>13,52; 15,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,43; 13,14</t>
+          <t>11,42; 13,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,75; 12,3</t>
+          <t>10,67; 12,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,31</t>
+          <t>12,78; 18,07</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13,92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,9</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,85</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12,97</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>14,04</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,02</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,53</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,92</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,9</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,85</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>13,72</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,16</t>
+          <t>13,31</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,58; 14,57</t>
+          <t>13,45; 14,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,6</t>
+          <t>11,37; 12,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,07; 12,07</t>
+          <t>11,33; 12,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,59</t>
+          <t>11,65; 14,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,46; 14,6</t>
+          <t>13,53; 14,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,49</t>
+          <t>11,47; 12,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 12,47</t>
+          <t>11,08; 12,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,61; 14,21</t>
+          <t>11,96; 16,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,67; 14,39</t>
+          <t>13,63; 14,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,58; 12,35</t>
+          <t>11,59; 12,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,36; 12,1</t>
+          <t>11,32; 12,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,12; 14,64</t>
+          <t>12,14; 14,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>13,51</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11,52</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,16</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,81</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,46</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9,25</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13,34</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11,66</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11,62</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,62</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>13.50989267260971</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>11.52081272154666</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>11.79292143682583</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>12.01993255712592</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>13.1575629819842</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>11.80890723819019</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>11.46482817271205</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>9.254129236053197</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>13.34182486324708</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>11.6643892996095</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>11.62441726188663</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>10.62405237627378</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12,28; 15,23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10,62; 12,85</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10,7; 13,28</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10,49; 13,56</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11,97; 14,39</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,91; 12,95</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,71; 12,5</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7,67; 11,1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12,55; 14,44</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11,02; 12,51</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10,95; 12,38</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,49; 11,84</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>12.27808876290421</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>10.61972801436729</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>10.69702823523025</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>10.48694937654327</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>11.96889842518873</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>10.90661670008512</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>10.709804075103</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>7.666781644160505</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>12.5530925795892</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>11.01930928311801</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>10.94745296074463</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>9.490946995808322</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>15.23099027905099</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.84510776682305</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>13.28149306990091</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>13.56036027122679</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>14.38997024945358</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>12.94725165361564</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>12.49601055174047</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>11.09674433941679</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>14.43508637125086</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>12.50835658503731</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>12.37738353469226</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>11.8379134778436</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13,64</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11,88</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11,31</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,28</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,14</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,81</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,07</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15,62</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13,89</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>11,85</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11,65</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,86</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>12,93; 14,54</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11,02; 13,05</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10,61; 12,38</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10,34; 14,21</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,39; 15,05</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,98; 13,0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,2; 13,22</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11,51; 23,28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13,38; 14,52</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11,18; 12,59</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11,05; 12,35</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,75; 17,81</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>13.63974280619689</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>11.88317003523918</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>11.31151242580332</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>12.27871955605484</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>14.13846678027707</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>11.80975087374075</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>12.06986960971746</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>15.62059370199327</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>13.89000545769331</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>11.84894887624698</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>11.65366812325264</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>13.86135217348604</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>14,52</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11,79</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,97</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13,72</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,17</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,63</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,12</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14,35</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12,21</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12,04</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,55</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>12.93241125595416</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>11.02196584897325</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>10.60755456144502</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>10.33929998385493</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>13.39281651139836</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>10.97968494143684</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>11.19700228092622</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>11.50840278030713</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>13.37835994677712</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>11.18185568611628</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>11.05393642571971</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>11.75233379677573</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>13,28; 16,27</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10,91; 13,04</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10,99; 13,54</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>10,89; 18,77</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>13,09; 15,31</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>11,36; 14,47</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,21; 13,46</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9,31; 14,41</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>13,53; 15,48</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>11,41; 13,31</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>11,29; 12,97</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>10,72; 15,44</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>14.54378102571301</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>13.05451155992204</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>12.38257166002942</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>14.21099563664765</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>15.05366802757302</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>13.000578051396</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>13.22226745501779</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>23.28052797136721</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>14.5196004290142</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>12.58686782341151</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>12.34789803698338</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>17.81114463872034</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14,18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12,38</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12,66</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,38</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,94</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,19</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17,42</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14,28</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12,17</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11,4</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>14,84</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>14.51786253378237</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>11.78895457386528</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>11.96533556121344</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>13.72216317790613</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>14.17319712068126</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>12.62686310463725</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>12.11621788298281</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>11.1379362846434</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>14.34853259118799</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>12.21156885615362</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>12.0407737140682</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>12.54525142896787</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>13,21; 15,51</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11,36; 13,67</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11,58; 14,1</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11,27; 16,47</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13,55; 15,69</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,88; 13,46</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,45; 11,03</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13,6; 23,61</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13,52; 15,11</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>11,42; 13,21</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>10,67; 12,27</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>12,78; 18,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>13.28129248338326</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>10.90571265118533</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>10.99286636392295</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>10.89184593884426</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>13.09113593186952</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>11.35544688682985</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>11.21073625280482</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>9.310332319530177</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>13.52631333896026</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>11.4095445075658</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>11.2911947974478</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>10.71562131998581</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>16.26955326114888</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.0403329956722</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>13.54429043934802</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>18.77068079747628</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>15.3091914100406</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>14.46858269323212</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>13.45524879756557</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>14.41378468221807</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>15.48255099949457</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>13.30789488467115</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>12.96720591241425</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>15.44017437566871</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>14.18114118439936</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>12.37664767564423</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>12.66025163065177</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>13.15080418967877</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>14.38134338109269</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>11.94483205434349</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>10.19073046116467</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>17.41964972153702</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>14.27807187721025</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>12.16797413807182</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>11.40441892477233</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>14.84182572460597</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>13.2069689850947</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>11.36399964973313</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>11.58324007556216</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>11.26925528381491</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>13.55018851976187</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>10.88362873513529</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>9.452257076503614</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>13.60186268190735</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>13.51726753678935</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>11.42305784967645</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>10.66823362922022</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>12.78465980388573</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>15.50610268120881</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>13.67490018672768</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>14.10289491412273</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>16.47353354502786</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>15.68633543663132</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>13.45935032264958</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>11.02679169862093</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>23.60990737092636</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>15.11285073075065</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>13.20544743487013</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>12.27307000938786</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>18.07103341462291</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>13,92</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11,9</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12,97</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,04</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,53</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13,72</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>13,98</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>11,96</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11,69</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>13,45; 14,51</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11,37; 12,5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11,33; 12,45</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11,65; 14,71</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,53; 14,59</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,47; 12,65</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,08; 12,07</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11,96; 16,86</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13,63; 14,37</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11,59; 12,38</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11,32; 12,11</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,14; 14,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>13.92103071657277</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>11.90391717788057</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>11.85040433136647</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>12.96750362173543</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>14.04437981032134</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>12.02288604179287</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>11.52944666064165</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>13.71931023165148</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>13.98157981034621</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>11.96161509590315</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>11.693703793222</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>13.30503018326292</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>13.44890842173381</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>11.37385004840927</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>11.33343395249603</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>11.6506891724136</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>13.53059226186534</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>11.46951661894438</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>11.08401096954695</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>11.95575165745194</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>13.62618824079139</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>11.58538125561825</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>11.32382013119831</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>12.13938202892009</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>14.50898756321102</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>12.49966560736521</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>12.44983585425031</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>14.70568462762993</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>14.58879493748012</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>12.65209444523252</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>12.0732040857605</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>16.85542541423531</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>14.37008663748824</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>12.37816765986172</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>12.11308658897577</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>14.82787926282703</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
